--- a/2022 data/excel_outputs/219_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/219_boothwise_data.xlsx
@@ -14,11 +14,86 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="627">
   <si>
     <t>AC 219 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -1600,7 +1675,7 @@
     <t>praathmik vighaaly cndrkuaa koNc</t>
   </si>
   <si>
-    <t>####### ###### ######## ###### ####### #####</t>
+    <t>praathmik vighaaly cndrkuaa koNc ROOM NO. 529</t>
   </si>
   <si>
     <t>shrii naathuuraam purohit baalikaa vighaaly</t>
@@ -1826,8 +1901,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1843,7 +1926,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1851,12 +1934,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2155,88 +2256,163 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>578</v>
+        <v>603</v>
       </c>
       <c r="D2" t="s">
-        <v>579</v>
+        <v>604</v>
       </c>
       <c r="E2" t="s">
-        <v>580</v>
+        <v>605</v>
       </c>
       <c r="F2" t="s">
-        <v>581</v>
+        <v>606</v>
       </c>
       <c r="G2" t="s">
-        <v>582</v>
+        <v>607</v>
       </c>
       <c r="H2" t="s">
-        <v>583</v>
+        <v>608</v>
       </c>
       <c r="I2" t="s">
-        <v>584</v>
+        <v>609</v>
       </c>
       <c r="J2" t="s">
-        <v>585</v>
+        <v>610</v>
       </c>
       <c r="K2" t="s">
-        <v>586</v>
+        <v>611</v>
       </c>
       <c r="L2" t="s">
-        <v>587</v>
+        <v>612</v>
       </c>
       <c r="M2" t="s">
-        <v>588</v>
+        <v>613</v>
       </c>
       <c r="N2" t="s">
-        <v>589</v>
+        <v>614</v>
       </c>
       <c r="O2" t="s">
-        <v>590</v>
+        <v>615</v>
       </c>
       <c r="P2" t="s">
-        <v>591</v>
+        <v>616</v>
       </c>
       <c r="Q2" t="s">
-        <v>592</v>
+        <v>617</v>
       </c>
       <c r="R2" t="s">
-        <v>593</v>
+        <v>618</v>
       </c>
       <c r="S2" t="s">
-        <v>594</v>
+        <v>619</v>
       </c>
       <c r="T2" t="s">
-        <v>595</v>
+        <v>620</v>
       </c>
       <c r="U2" t="s">
-        <v>596</v>
+        <v>621</v>
       </c>
       <c r="V2" t="s">
-        <v>597</v>
+        <v>622</v>
       </c>
       <c r="W2" t="s">
-        <v>598</v>
+        <v>623</v>
       </c>
       <c r="X2" t="s">
-        <v>599</v>
+        <v>624</v>
       </c>
       <c r="Y2" t="s">
-        <v>600</v>
+        <v>625</v>
       </c>
       <c r="Z2" t="s">
-        <v>601</v>
+        <v>626</v>
       </c>
     </row>
     <row r="3" spans="1:26">
@@ -2244,7 +2420,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -2324,7 +2500,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -2404,7 +2580,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -2484,7 +2660,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -2564,7 +2740,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -2644,7 +2820,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -2724,7 +2900,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -2804,7 +2980,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -2884,7 +3060,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -2964,7 +3140,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -3044,7 +3220,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -3124,7 +3300,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -3204,7 +3380,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -3284,7 +3460,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -3364,7 +3540,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -3444,7 +3620,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -3524,7 +3700,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -3604,7 +3780,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -3684,7 +3860,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -3764,7 +3940,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -3844,7 +4020,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -3924,7 +4100,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -4004,7 +4180,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -4084,7 +4260,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -4164,7 +4340,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -4244,7 +4420,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -4324,7 +4500,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -4404,7 +4580,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -4484,7 +4660,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -4564,7 +4740,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -4644,7 +4820,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -4724,7 +4900,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -4804,7 +4980,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -4884,7 +5060,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -4964,7 +5140,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -5044,7 +5220,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -5124,7 +5300,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -5204,7 +5380,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -5284,7 +5460,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -5364,7 +5540,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -5444,7 +5620,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -5524,7 +5700,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -5604,7 +5780,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -5684,7 +5860,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -5764,7 +5940,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -5844,7 +6020,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -5924,7 +6100,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -6004,7 +6180,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -6084,7 +6260,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -6164,7 +6340,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -6244,7 +6420,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -6324,7 +6500,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -6404,7 +6580,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -6484,7 +6660,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -6564,7 +6740,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -6644,7 +6820,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -6724,7 +6900,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -6804,7 +6980,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -6884,7 +7060,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -6964,7 +7140,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -7044,7 +7220,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -7124,7 +7300,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -7204,7 +7380,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -7284,7 +7460,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -7364,7 +7540,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -7444,7 +7620,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -7524,7 +7700,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -7604,7 +7780,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -7684,7 +7860,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -7764,7 +7940,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -7844,7 +8020,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -7924,7 +8100,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -8004,7 +8180,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -8084,7 +8260,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -8164,7 +8340,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -8244,7 +8420,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -8324,7 +8500,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -8404,7 +8580,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -8484,7 +8660,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -8564,7 +8740,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -8644,7 +8820,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -8724,7 +8900,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -8804,7 +8980,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -8884,7 +9060,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -8964,7 +9140,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -9044,7 +9220,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -9124,7 +9300,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -9204,7 +9380,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -9284,7 +9460,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -9364,7 +9540,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -9444,7 +9620,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -9524,7 +9700,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -9604,7 +9780,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -9684,7 +9860,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -9764,7 +9940,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -9844,7 +10020,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -9924,7 +10100,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -10004,7 +10180,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -10084,7 +10260,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -10164,7 +10340,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -10244,7 +10420,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -10324,7 +10500,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -10404,7 +10580,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -10484,7 +10660,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -10564,7 +10740,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -10644,7 +10820,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -10724,7 +10900,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -10804,7 +10980,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -10884,7 +11060,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -10964,7 +11140,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -11044,7 +11220,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -11124,7 +11300,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -11204,7 +11380,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -11284,7 +11460,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -11364,7 +11540,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -11444,7 +11620,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -11524,7 +11700,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -11604,7 +11780,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -11684,7 +11860,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -11764,7 +11940,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -11844,7 +12020,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -11924,7 +12100,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -12004,7 +12180,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -12084,7 +12260,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -12164,7 +12340,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -12244,7 +12420,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -12324,7 +12500,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -12404,7 +12580,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -12484,7 +12660,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -12564,7 +12740,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -12644,7 +12820,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -12724,7 +12900,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -12804,7 +12980,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -12884,7 +13060,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -12964,7 +13140,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -13044,7 +13220,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -13124,7 +13300,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -13204,7 +13380,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -13284,7 +13460,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -13364,7 +13540,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -13444,7 +13620,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -13524,7 +13700,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -13604,7 +13780,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -13684,7 +13860,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -13764,7 +13940,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -13844,7 +14020,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -13924,7 +14100,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -14004,7 +14180,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -14084,7 +14260,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -14164,7 +14340,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -14244,7 +14420,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -14324,7 +14500,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -14404,7 +14580,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -14484,7 +14660,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -14564,7 +14740,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -14644,7 +14820,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -14724,7 +14900,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -14804,7 +14980,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -14884,7 +15060,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -14964,7 +15140,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -15044,7 +15220,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -15124,7 +15300,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -15204,7 +15380,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -15284,7 +15460,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -15364,7 +15540,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -15444,7 +15620,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -15524,7 +15700,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -15604,7 +15780,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -15684,7 +15860,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -15764,7 +15940,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -15844,7 +16020,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -15924,7 +16100,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -16004,7 +16180,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -16084,7 +16260,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -16164,7 +16340,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -16244,7 +16420,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -16324,7 +16500,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -16404,7 +16580,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -16484,7 +16660,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -16564,7 +16740,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -16644,7 +16820,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -16724,7 +16900,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -16804,7 +16980,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -16884,7 +17060,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -16964,7 +17140,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -17044,7 +17220,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -17124,7 +17300,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -17204,7 +17380,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="C190">
         <v>0</v>
@@ -17284,7 +17460,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -17364,7 +17540,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="C192">
         <v>0</v>
@@ -17444,7 +17620,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="C193">
         <v>0</v>
@@ -17524,7 +17700,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="C194">
         <v>0</v>
@@ -17604,7 +17780,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="C195">
         <v>0</v>
@@ -17684,7 +17860,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -17764,7 +17940,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -17844,7 +18020,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -17924,7 +18100,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -18004,7 +18180,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -18084,7 +18260,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -18164,7 +18340,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="C202">
         <v>0</v>
@@ -18244,7 +18420,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -18324,7 +18500,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -18404,7 +18580,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="C205">
         <v>0</v>
@@ -18484,7 +18660,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -18564,7 +18740,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -18644,7 +18820,7 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="C208">
         <v>0</v>
@@ -18724,7 +18900,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="C209">
         <v>0</v>
@@ -18804,7 +18980,7 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -18884,7 +19060,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="C211">
         <v>0</v>
@@ -18964,7 +19140,7 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="C212">
         <v>0</v>
@@ -19044,7 +19220,7 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -19124,7 +19300,7 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>214</v>
+        <v>239</v>
       </c>
       <c r="C214">
         <v>0</v>
@@ -19204,7 +19380,7 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C215">
         <v>0</v>
@@ -19284,7 +19460,7 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -19364,7 +19540,7 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="C217">
         <v>0</v>
@@ -19444,7 +19620,7 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="C218">
         <v>0</v>
@@ -19524,7 +19700,7 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="C219">
         <v>0</v>
@@ -19604,7 +19780,7 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="C220">
         <v>0</v>
@@ -19684,7 +19860,7 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="C221">
         <v>0</v>
@@ -19764,7 +19940,7 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="C222">
         <v>0</v>
@@ -19844,7 +20020,7 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="C223">
         <v>0</v>
@@ -19924,7 +20100,7 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="C224">
         <v>0</v>
@@ -20004,7 +20180,7 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="C225">
         <v>0</v>
@@ -20084,7 +20260,7 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -20164,7 +20340,7 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -20244,7 +20420,7 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>228</v>
+        <v>253</v>
       </c>
       <c r="C228">
         <v>0</v>
@@ -20324,7 +20500,7 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="C229">
         <v>0</v>
@@ -20404,7 +20580,7 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="C230">
         <v>0</v>
@@ -20484,7 +20660,7 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="C231">
         <v>0</v>
@@ -20564,7 +20740,7 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="C232">
         <v>0</v>
@@ -20644,7 +20820,7 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="C233">
         <v>0</v>
@@ -20724,7 +20900,7 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="C234">
         <v>0</v>
@@ -20804,7 +20980,7 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="C235">
         <v>0</v>
@@ -20884,7 +21060,7 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="C236">
         <v>0</v>
@@ -20964,7 +21140,7 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="C237">
         <v>0</v>
@@ -21044,7 +21220,7 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -21124,7 +21300,7 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="C239">
         <v>0</v>
@@ -21204,7 +21380,7 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="C240">
         <v>0</v>
@@ -21284,7 +21460,7 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="C241">
         <v>0</v>
@@ -21364,7 +21540,7 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="C242">
         <v>0</v>
@@ -21444,7 +21620,7 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="C243">
         <v>0</v>
@@ -21524,7 +21700,7 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>244</v>
+        <v>269</v>
       </c>
       <c r="C244">
         <v>0</v>
@@ -21604,7 +21780,7 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="C245">
         <v>0</v>
@@ -21684,7 +21860,7 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="C246">
         <v>0</v>
@@ -21764,7 +21940,7 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>247</v>
+        <v>272</v>
       </c>
       <c r="C247">
         <v>0</v>
@@ -21844,7 +22020,7 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="C248">
         <v>0</v>
@@ -21924,7 +22100,7 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="C249">
         <v>0</v>
@@ -22004,7 +22180,7 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="C250">
         <v>0</v>
@@ -22084,7 +22260,7 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="C251">
         <v>0</v>
@@ -22164,7 +22340,7 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="C252">
         <v>0</v>
@@ -22244,7 +22420,7 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="C253">
         <v>0</v>
@@ -22324,7 +22500,7 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="C254">
         <v>0</v>
@@ -22404,7 +22580,7 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="C255">
         <v>0</v>
@@ -22484,7 +22660,7 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>256</v>
+        <v>281</v>
       </c>
       <c r="C256">
         <v>0</v>
@@ -22564,7 +22740,7 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>257</v>
+        <v>282</v>
       </c>
       <c r="C257">
         <v>0</v>
@@ -22644,7 +22820,7 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>258</v>
+        <v>283</v>
       </c>
       <c r="C258">
         <v>0</v>
@@ -22724,7 +22900,7 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="C259">
         <v>0</v>
@@ -22804,7 +22980,7 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="C260">
         <v>0</v>
@@ -22884,7 +23060,7 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="C261">
         <v>0</v>
@@ -22964,7 +23140,7 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="C262">
         <v>0</v>
@@ -23044,7 +23220,7 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="C263">
         <v>0</v>
@@ -23124,7 +23300,7 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="C264">
         <v>0</v>
@@ -23204,7 +23380,7 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="C265">
         <v>0</v>
@@ -23284,7 +23460,7 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="C266">
         <v>0</v>
@@ -23364,7 +23540,7 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="C267">
         <v>0</v>
@@ -23444,7 +23620,7 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="C268">
         <v>0</v>
@@ -23524,7 +23700,7 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>269</v>
+        <v>294</v>
       </c>
       <c r="C269">
         <v>0</v>
@@ -23604,7 +23780,7 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>270</v>
+        <v>295</v>
       </c>
       <c r="C270">
         <v>0</v>
@@ -23684,7 +23860,7 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="C271">
         <v>0</v>
@@ -23764,7 +23940,7 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>272</v>
+        <v>297</v>
       </c>
       <c r="C272">
         <v>0</v>
@@ -23844,7 +24020,7 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>273</v>
+        <v>298</v>
       </c>
       <c r="C273">
         <v>0</v>
@@ -23924,7 +24100,7 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c r="C274">
         <v>0</v>
@@ -24004,7 +24180,7 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="C275">
         <v>0</v>
@@ -24084,7 +24260,7 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="C276">
         <v>0</v>
@@ -24164,7 +24340,7 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>277</v>
+        <v>302</v>
       </c>
       <c r="C277">
         <v>0</v>
@@ -24244,7 +24420,7 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>278</v>
+        <v>303</v>
       </c>
       <c r="C278">
         <v>0</v>
@@ -24324,7 +24500,7 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>279</v>
+        <v>304</v>
       </c>
       <c r="C279">
         <v>0</v>
@@ -24404,7 +24580,7 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="C280">
         <v>0</v>
@@ -24484,7 +24660,7 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>281</v>
+        <v>306</v>
       </c>
       <c r="C281">
         <v>0</v>
@@ -24564,7 +24740,7 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="C282">
         <v>0</v>
@@ -24644,7 +24820,7 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="C283">
         <v>0</v>
@@ -24724,7 +24900,7 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="C284">
         <v>0</v>
@@ -24804,7 +24980,7 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="C285">
         <v>0</v>
@@ -24884,7 +25060,7 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="C286">
         <v>0</v>
@@ -24964,7 +25140,7 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="C287">
         <v>0</v>
@@ -25044,7 +25220,7 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>288</v>
+        <v>313</v>
       </c>
       <c r="C288">
         <v>0</v>
@@ -25124,7 +25300,7 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>289</v>
+        <v>314</v>
       </c>
       <c r="C289">
         <v>0</v>
@@ -25204,7 +25380,7 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="C290">
         <v>0</v>
@@ -25284,7 +25460,7 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>291</v>
+        <v>316</v>
       </c>
       <c r="C291">
         <v>0</v>
@@ -25364,7 +25540,7 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="C292">
         <v>0</v>
@@ -25444,7 +25620,7 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
       <c r="C293">
         <v>0</v>
@@ -25524,7 +25700,7 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="C294">
         <v>0</v>
@@ -25604,7 +25780,7 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>295</v>
+        <v>320</v>
       </c>
       <c r="C295">
         <v>0</v>
@@ -25684,7 +25860,7 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>296</v>
+        <v>321</v>
       </c>
       <c r="C296">
         <v>0</v>
@@ -25764,7 +25940,7 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="C297">
         <v>0</v>
@@ -25844,7 +26020,7 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>298</v>
+        <v>323</v>
       </c>
       <c r="C298">
         <v>0</v>
@@ -25924,7 +26100,7 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>299</v>
+        <v>324</v>
       </c>
       <c r="C299">
         <v>0</v>
@@ -26004,7 +26180,7 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="C300">
         <v>0</v>
@@ -26084,7 +26260,7 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="C301">
         <v>0</v>
@@ -26164,7 +26340,7 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="C302">
         <v>0</v>
@@ -26244,7 +26420,7 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="C303">
         <v>0</v>
@@ -26324,7 +26500,7 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>304</v>
+        <v>329</v>
       </c>
       <c r="C304">
         <v>0</v>
@@ -26404,7 +26580,7 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>305</v>
+        <v>330</v>
       </c>
       <c r="C305">
         <v>0</v>
@@ -26484,7 +26660,7 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="C306">
         <v>0</v>
@@ -26564,7 +26740,7 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>307</v>
+        <v>332</v>
       </c>
       <c r="C307">
         <v>0</v>
@@ -26644,7 +26820,7 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>308</v>
+        <v>333</v>
       </c>
       <c r="C308">
         <v>0</v>
@@ -26724,7 +26900,7 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>309</v>
+        <v>334</v>
       </c>
       <c r="C309">
         <v>0</v>
@@ -26804,7 +26980,7 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="C310">
         <v>0</v>
@@ -26884,7 +27060,7 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>311</v>
+        <v>336</v>
       </c>
       <c r="C311">
         <v>0</v>
@@ -26964,7 +27140,7 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="C312">
         <v>0</v>
@@ -27044,7 +27220,7 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="C313">
         <v>0</v>
@@ -27124,7 +27300,7 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="C314">
         <v>0</v>
@@ -27204,7 +27380,7 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="C315">
         <v>0</v>
@@ -27284,7 +27460,7 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
       <c r="C316">
         <v>0</v>
@@ -27364,7 +27540,7 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
       <c r="C317">
         <v>0</v>
@@ -27444,7 +27620,7 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="C318">
         <v>0</v>
@@ -27524,7 +27700,7 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="C319">
         <v>0</v>
@@ -27604,7 +27780,7 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="C320">
         <v>0</v>
@@ -27684,7 +27860,7 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="C321">
         <v>0</v>
@@ -27764,7 +27940,7 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="C322">
         <v>0</v>
@@ -27844,7 +28020,7 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="C323">
         <v>0</v>
@@ -27924,7 +28100,7 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>323</v>
+        <v>348</v>
       </c>
       <c r="C324">
         <v>0</v>
@@ -28004,7 +28180,7 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="C325">
         <v>0</v>
@@ -28084,7 +28260,7 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="C326">
         <v>0</v>
@@ -28164,7 +28340,7 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="C327">
         <v>0</v>
@@ -28244,7 +28420,7 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="C328">
         <v>0</v>
@@ -28324,7 +28500,7 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>328</v>
+        <v>353</v>
       </c>
       <c r="C329">
         <v>0</v>
@@ -28404,7 +28580,7 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="C330">
         <v>0</v>
@@ -28484,7 +28660,7 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="C331">
         <v>0</v>
@@ -28564,7 +28740,7 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>331</v>
+        <v>356</v>
       </c>
       <c r="C332">
         <v>0</v>
@@ -28644,7 +28820,7 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>332</v>
+        <v>357</v>
       </c>
       <c r="C333">
         <v>0</v>
@@ -28724,7 +28900,7 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>333</v>
+        <v>358</v>
       </c>
       <c r="C334">
         <v>0</v>
@@ -28804,7 +28980,7 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C335">
         <v>0</v>
@@ -28884,7 +29060,7 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="C336">
         <v>0</v>
@@ -28964,7 +29140,7 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>335</v>
+        <v>360</v>
       </c>
       <c r="C337">
         <v>0</v>
@@ -29044,7 +29220,7 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>336</v>
+        <v>361</v>
       </c>
       <c r="C338">
         <v>0</v>
@@ -29124,7 +29300,7 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>337</v>
+        <v>362</v>
       </c>
       <c r="C339">
         <v>0</v>
@@ -29204,7 +29380,7 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>338</v>
+        <v>363</v>
       </c>
       <c r="C340">
         <v>0</v>
@@ -29284,7 +29460,7 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>339</v>
+        <v>364</v>
       </c>
       <c r="C341">
         <v>0</v>
@@ -29364,7 +29540,7 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>340</v>
+        <v>365</v>
       </c>
       <c r="C342">
         <v>0</v>
@@ -29444,7 +29620,7 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>341</v>
+        <v>366</v>
       </c>
       <c r="C343">
         <v>0</v>
@@ -29524,7 +29700,7 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="C344">
         <v>0</v>
@@ -29604,7 +29780,7 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>343</v>
+        <v>368</v>
       </c>
       <c r="C345">
         <v>0</v>
@@ -29684,7 +29860,7 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>344</v>
+        <v>369</v>
       </c>
       <c r="C346">
         <v>0</v>
@@ -29764,7 +29940,7 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>345</v>
+        <v>370</v>
       </c>
       <c r="C347">
         <v>0</v>
@@ -29844,7 +30020,7 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>346</v>
+        <v>371</v>
       </c>
       <c r="C348">
         <v>0</v>
@@ -29924,7 +30100,7 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="C349">
         <v>0</v>
@@ -30004,7 +30180,7 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>348</v>
+        <v>373</v>
       </c>
       <c r="C350">
         <v>0</v>
@@ -30084,7 +30260,7 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>349</v>
+        <v>374</v>
       </c>
       <c r="C351">
         <v>0</v>
@@ -30164,7 +30340,7 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="C352">
         <v>0</v>
@@ -30244,7 +30420,7 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>351</v>
+        <v>376</v>
       </c>
       <c r="C353">
         <v>0</v>
@@ -30324,7 +30500,7 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="C354">
         <v>0</v>
@@ -30404,7 +30580,7 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="C355">
         <v>0</v>
@@ -30484,7 +30660,7 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>354</v>
+        <v>379</v>
       </c>
       <c r="C356">
         <v>0</v>
@@ -30564,7 +30740,7 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>355</v>
+        <v>380</v>
       </c>
       <c r="C357">
         <v>0</v>
@@ -30644,7 +30820,7 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C358">
         <v>0</v>
@@ -30724,7 +30900,7 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>357</v>
+        <v>382</v>
       </c>
       <c r="C359">
         <v>0</v>
@@ -30804,7 +30980,7 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>358</v>
+        <v>383</v>
       </c>
       <c r="C360">
         <v>0</v>
@@ -30884,7 +31060,7 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="C361">
         <v>0</v>
@@ -30964,7 +31140,7 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>360</v>
+        <v>385</v>
       </c>
       <c r="C362">
         <v>0</v>
@@ -31044,7 +31220,7 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>361</v>
+        <v>386</v>
       </c>
       <c r="C363">
         <v>0</v>
@@ -31124,7 +31300,7 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>362</v>
+        <v>387</v>
       </c>
       <c r="C364">
         <v>0</v>
@@ -31204,7 +31380,7 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>363</v>
+        <v>388</v>
       </c>
       <c r="C365">
         <v>0</v>
@@ -31284,7 +31460,7 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>364</v>
+        <v>389</v>
       </c>
       <c r="C366">
         <v>0</v>
@@ -31364,7 +31540,7 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>365</v>
+        <v>390</v>
       </c>
       <c r="C367">
         <v>0</v>
@@ -31444,7 +31620,7 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="C368">
         <v>0</v>
@@ -31524,7 +31700,7 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>367</v>
+        <v>392</v>
       </c>
       <c r="C369">
         <v>0</v>
@@ -31604,7 +31780,7 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>368</v>
+        <v>393</v>
       </c>
       <c r="C370">
         <v>0</v>
@@ -31684,7 +31860,7 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>369</v>
+        <v>394</v>
       </c>
       <c r="C371">
         <v>0</v>
@@ -31764,7 +31940,7 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="C372">
         <v>0</v>
@@ -31844,7 +32020,7 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="C373">
         <v>0</v>
@@ -31924,7 +32100,7 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>372</v>
+        <v>397</v>
       </c>
       <c r="C374">
         <v>0</v>
@@ -32004,7 +32180,7 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>373</v>
+        <v>398</v>
       </c>
       <c r="C375">
         <v>0</v>
@@ -32084,7 +32260,7 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="C376">
         <v>0</v>
@@ -32164,7 +32340,7 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="C377">
         <v>0</v>
@@ -32244,7 +32420,7 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>376</v>
+        <v>401</v>
       </c>
       <c r="C378">
         <v>0</v>
@@ -32324,7 +32500,7 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="C379">
         <v>0</v>
@@ -32404,7 +32580,7 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="C380">
         <v>0</v>
@@ -32484,7 +32660,7 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>379</v>
+        <v>404</v>
       </c>
       <c r="C381">
         <v>0</v>
@@ -32564,7 +32740,7 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="C382">
         <v>0</v>
@@ -32644,7 +32820,7 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>381</v>
+        <v>406</v>
       </c>
       <c r="C383">
         <v>0</v>
@@ -32724,7 +32900,7 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>382</v>
+        <v>407</v>
       </c>
       <c r="C384">
         <v>0</v>
@@ -32804,7 +32980,7 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="C385">
         <v>0</v>
@@ -32884,7 +33060,7 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>384</v>
+        <v>409</v>
       </c>
       <c r="C386">
         <v>0</v>
@@ -32964,7 +33140,7 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>385</v>
+        <v>410</v>
       </c>
       <c r="C387">
         <v>0</v>
@@ -33044,7 +33220,7 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>386</v>
+        <v>411</v>
       </c>
       <c r="C388">
         <v>0</v>
@@ -33124,7 +33300,7 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>387</v>
+        <v>412</v>
       </c>
       <c r="C389">
         <v>0</v>
@@ -33204,7 +33380,7 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>388</v>
+        <v>413</v>
       </c>
       <c r="C390">
         <v>0</v>
@@ -33284,7 +33460,7 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>389</v>
+        <v>414</v>
       </c>
       <c r="C391">
         <v>0</v>
@@ -33364,7 +33540,7 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="C392">
         <v>0</v>
@@ -33444,7 +33620,7 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>391</v>
+        <v>416</v>
       </c>
       <c r="C393">
         <v>0</v>
@@ -33524,7 +33700,7 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="C394">
         <v>0</v>
@@ -33604,7 +33780,7 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>393</v>
+        <v>418</v>
       </c>
       <c r="C395">
         <v>0</v>
@@ -33684,7 +33860,7 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>394</v>
+        <v>419</v>
       </c>
       <c r="C396">
         <v>0</v>
@@ -33764,7 +33940,7 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="C397">
         <v>0</v>
@@ -33844,7 +34020,7 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>396</v>
+        <v>421</v>
       </c>
       <c r="C398">
         <v>0</v>
@@ -33924,7 +34100,7 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="C399">
         <v>0</v>
@@ -34004,7 +34180,7 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>398</v>
+        <v>423</v>
       </c>
       <c r="C400">
         <v>0</v>
@@ -34084,7 +34260,7 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="C401">
         <v>0</v>
@@ -34164,7 +34340,7 @@
         <v>401</v>
       </c>
       <c r="B402" t="s">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="C402">
         <v>0</v>
@@ -34244,7 +34420,7 @@
         <v>402</v>
       </c>
       <c r="B403" t="s">
-        <v>401</v>
+        <v>426</v>
       </c>
       <c r="C403">
         <v>0</v>
@@ -34324,7 +34500,7 @@
         <v>403</v>
       </c>
       <c r="B404" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="C404">
         <v>0</v>
@@ -34404,7 +34580,7 @@
         <v>404</v>
       </c>
       <c r="B405" t="s">
-        <v>403</v>
+        <v>428</v>
       </c>
       <c r="C405">
         <v>0</v>
@@ -34484,7 +34660,7 @@
         <v>405</v>
       </c>
       <c r="B406" t="s">
-        <v>404</v>
+        <v>429</v>
       </c>
       <c r="C406">
         <v>0</v>
@@ -34564,7 +34740,7 @@
         <v>406</v>
       </c>
       <c r="B407" t="s">
-        <v>405</v>
+        <v>430</v>
       </c>
       <c r="C407">
         <v>0</v>
@@ -34644,7 +34820,7 @@
         <v>407</v>
       </c>
       <c r="B408" t="s">
-        <v>406</v>
+        <v>431</v>
       </c>
       <c r="C408">
         <v>0</v>
@@ -34724,7 +34900,7 @@
         <v>408</v>
       </c>
       <c r="B409" t="s">
-        <v>407</v>
+        <v>432</v>
       </c>
       <c r="C409">
         <v>0</v>
@@ -34804,7 +34980,7 @@
         <v>409</v>
       </c>
       <c r="B410" t="s">
-        <v>408</v>
+        <v>433</v>
       </c>
       <c r="C410">
         <v>0</v>
@@ -34884,7 +35060,7 @@
         <v>410</v>
       </c>
       <c r="B411" t="s">
-        <v>409</v>
+        <v>434</v>
       </c>
       <c r="C411">
         <v>0</v>
@@ -34964,7 +35140,7 @@
         <v>411</v>
       </c>
       <c r="B412" t="s">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="C412">
         <v>0</v>
@@ -35044,7 +35220,7 @@
         <v>412</v>
       </c>
       <c r="B413" t="s">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="C413">
         <v>0</v>
@@ -35124,7 +35300,7 @@
         <v>413</v>
       </c>
       <c r="B414" t="s">
-        <v>412</v>
+        <v>437</v>
       </c>
       <c r="C414">
         <v>0</v>
@@ -35204,7 +35380,7 @@
         <v>414</v>
       </c>
       <c r="B415" t="s">
-        <v>413</v>
+        <v>438</v>
       </c>
       <c r="C415">
         <v>0</v>
@@ -35284,7 +35460,7 @@
         <v>415</v>
       </c>
       <c r="B416" t="s">
-        <v>414</v>
+        <v>439</v>
       </c>
       <c r="C416">
         <v>0</v>
@@ -35364,7 +35540,7 @@
         <v>416</v>
       </c>
       <c r="B417" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="C417">
         <v>0</v>
@@ -35444,7 +35620,7 @@
         <v>417</v>
       </c>
       <c r="B418" t="s">
-        <v>416</v>
+        <v>441</v>
       </c>
       <c r="C418">
         <v>0</v>
@@ -35524,7 +35700,7 @@
         <v>418</v>
       </c>
       <c r="B419" t="s">
-        <v>417</v>
+        <v>442</v>
       </c>
       <c r="C419">
         <v>0</v>
@@ -35604,7 +35780,7 @@
         <v>419</v>
       </c>
       <c r="B420" t="s">
-        <v>418</v>
+        <v>443</v>
       </c>
       <c r="C420">
         <v>0</v>
@@ -35684,7 +35860,7 @@
         <v>420</v>
       </c>
       <c r="B421" t="s">
-        <v>419</v>
+        <v>444</v>
       </c>
       <c r="C421">
         <v>0</v>
@@ -35764,7 +35940,7 @@
         <v>421</v>
       </c>
       <c r="B422" t="s">
-        <v>420</v>
+        <v>445</v>
       </c>
       <c r="C422">
         <v>0</v>
@@ -35844,7 +36020,7 @@
         <v>422</v>
       </c>
       <c r="B423" t="s">
-        <v>421</v>
+        <v>446</v>
       </c>
       <c r="C423">
         <v>0</v>
@@ -35924,7 +36100,7 @@
         <v>423</v>
       </c>
       <c r="B424" t="s">
-        <v>422</v>
+        <v>447</v>
       </c>
       <c r="C424">
         <v>0</v>
@@ -36004,7 +36180,7 @@
         <v>424</v>
       </c>
       <c r="B425" t="s">
-        <v>423</v>
+        <v>448</v>
       </c>
       <c r="C425">
         <v>0</v>
@@ -36084,7 +36260,7 @@
         <v>425</v>
       </c>
       <c r="B426" t="s">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="C426">
         <v>0</v>
@@ -36164,7 +36340,7 @@
         <v>426</v>
       </c>
       <c r="B427" t="s">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="C427">
         <v>0</v>
@@ -36244,7 +36420,7 @@
         <v>427</v>
       </c>
       <c r="B428" t="s">
-        <v>426</v>
+        <v>451</v>
       </c>
       <c r="C428">
         <v>0</v>
@@ -36324,7 +36500,7 @@
         <v>428</v>
       </c>
       <c r="B429" t="s">
-        <v>427</v>
+        <v>452</v>
       </c>
       <c r="C429">
         <v>0</v>
@@ -36404,7 +36580,7 @@
         <v>429</v>
       </c>
       <c r="B430" t="s">
-        <v>428</v>
+        <v>453</v>
       </c>
       <c r="C430">
         <v>0</v>
@@ -36484,7 +36660,7 @@
         <v>430</v>
       </c>
       <c r="B431" t="s">
-        <v>429</v>
+        <v>454</v>
       </c>
       <c r="C431">
         <v>0</v>
@@ -36564,7 +36740,7 @@
         <v>431</v>
       </c>
       <c r="B432" t="s">
-        <v>430</v>
+        <v>455</v>
       </c>
       <c r="C432">
         <v>0</v>
@@ -36644,7 +36820,7 @@
         <v>432</v>
       </c>
       <c r="B433" t="s">
-        <v>431</v>
+        <v>456</v>
       </c>
       <c r="C433">
         <v>0</v>
@@ -36724,7 +36900,7 @@
         <v>433</v>
       </c>
       <c r="B434" t="s">
-        <v>432</v>
+        <v>457</v>
       </c>
       <c r="C434">
         <v>0</v>
@@ -36804,7 +36980,7 @@
         <v>434</v>
       </c>
       <c r="B435" t="s">
-        <v>433</v>
+        <v>458</v>
       </c>
       <c r="C435">
         <v>0</v>
@@ -36884,7 +37060,7 @@
         <v>435</v>
       </c>
       <c r="B436" t="s">
-        <v>434</v>
+        <v>459</v>
       </c>
       <c r="C436">
         <v>0</v>
@@ -36964,7 +37140,7 @@
         <v>436</v>
       </c>
       <c r="B437" t="s">
-        <v>435</v>
+        <v>460</v>
       </c>
       <c r="C437">
         <v>0</v>
@@ -37044,7 +37220,7 @@
         <v>437</v>
       </c>
       <c r="B438" t="s">
-        <v>436</v>
+        <v>461</v>
       </c>
       <c r="C438">
         <v>0</v>
@@ -37124,7 +37300,7 @@
         <v>438</v>
       </c>
       <c r="B439" t="s">
-        <v>437</v>
+        <v>462</v>
       </c>
       <c r="C439">
         <v>0</v>
@@ -37204,7 +37380,7 @@
         <v>439</v>
       </c>
       <c r="B440" t="s">
-        <v>438</v>
+        <v>463</v>
       </c>
       <c r="C440">
         <v>0</v>
@@ -37284,7 +37460,7 @@
         <v>440</v>
       </c>
       <c r="B441" t="s">
-        <v>439</v>
+        <v>464</v>
       </c>
       <c r="C441">
         <v>0</v>
@@ -37364,7 +37540,7 @@
         <v>441</v>
       </c>
       <c r="B442" t="s">
-        <v>440</v>
+        <v>465</v>
       </c>
       <c r="C442">
         <v>0</v>
@@ -37444,7 +37620,7 @@
         <v>442</v>
       </c>
       <c r="B443" t="s">
-        <v>441</v>
+        <v>466</v>
       </c>
       <c r="C443">
         <v>0</v>
@@ -37524,7 +37700,7 @@
         <v>443</v>
       </c>
       <c r="B444" t="s">
-        <v>442</v>
+        <v>467</v>
       </c>
       <c r="C444">
         <v>0</v>
@@ -37604,7 +37780,7 @@
         <v>444</v>
       </c>
       <c r="B445" t="s">
-        <v>443</v>
+        <v>468</v>
       </c>
       <c r="C445">
         <v>0</v>
@@ -37684,7 +37860,7 @@
         <v>445</v>
       </c>
       <c r="B446" t="s">
-        <v>444</v>
+        <v>469</v>
       </c>
       <c r="C446">
         <v>0</v>
@@ -37764,7 +37940,7 @@
         <v>446</v>
       </c>
       <c r="B447" t="s">
-        <v>445</v>
+        <v>470</v>
       </c>
       <c r="C447">
         <v>0</v>
@@ -37844,7 +38020,7 @@
         <v>447</v>
       </c>
       <c r="B448" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="C448">
         <v>0</v>
@@ -37924,7 +38100,7 @@
         <v>448</v>
       </c>
       <c r="B449" t="s">
-        <v>447</v>
+        <v>472</v>
       </c>
       <c r="C449">
         <v>0</v>
@@ -38004,7 +38180,7 @@
         <v>449</v>
       </c>
       <c r="B450" t="s">
-        <v>448</v>
+        <v>473</v>
       </c>
       <c r="C450">
         <v>0</v>
@@ -38084,7 +38260,7 @@
         <v>450</v>
       </c>
       <c r="B451" t="s">
-        <v>449</v>
+        <v>474</v>
       </c>
       <c r="C451">
         <v>0</v>
@@ -38164,7 +38340,7 @@
         <v>451</v>
       </c>
       <c r="B452" t="s">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="C452">
         <v>0</v>
@@ -38244,7 +38420,7 @@
         <v>452</v>
       </c>
       <c r="B453" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="C453">
         <v>0</v>
@@ -38324,7 +38500,7 @@
         <v>453</v>
       </c>
       <c r="B454" t="s">
-        <v>452</v>
+        <v>477</v>
       </c>
       <c r="C454">
         <v>0</v>
@@ -38404,7 +38580,7 @@
         <v>454</v>
       </c>
       <c r="B455" t="s">
-        <v>453</v>
+        <v>478</v>
       </c>
       <c r="C455">
         <v>0</v>
@@ -38484,7 +38660,7 @@
         <v>455</v>
       </c>
       <c r="B456" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="C456">
         <v>0</v>
@@ -38564,7 +38740,7 @@
         <v>456</v>
       </c>
       <c r="B457" t="s">
-        <v>455</v>
+        <v>480</v>
       </c>
       <c r="C457">
         <v>0</v>
@@ -38644,7 +38820,7 @@
         <v>457</v>
       </c>
       <c r="B458" t="s">
-        <v>456</v>
+        <v>481</v>
       </c>
       <c r="C458">
         <v>0</v>
@@ -38724,7 +38900,7 @@
         <v>458</v>
       </c>
       <c r="B459" t="s">
-        <v>457</v>
+        <v>482</v>
       </c>
       <c r="C459">
         <v>0</v>
@@ -38804,7 +38980,7 @@
         <v>459</v>
       </c>
       <c r="B460" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="C460">
         <v>0</v>
@@ -38884,7 +39060,7 @@
         <v>460</v>
       </c>
       <c r="B461" t="s">
-        <v>459</v>
+        <v>484</v>
       </c>
       <c r="C461">
         <v>0</v>
@@ -38964,7 +39140,7 @@
         <v>461</v>
       </c>
       <c r="B462" t="s">
-        <v>460</v>
+        <v>485</v>
       </c>
       <c r="C462">
         <v>0</v>
@@ -39044,7 +39220,7 @@
         <v>462</v>
       </c>
       <c r="B463" t="s">
-        <v>461</v>
+        <v>486</v>
       </c>
       <c r="C463">
         <v>0</v>
@@ -39124,7 +39300,7 @@
         <v>463</v>
       </c>
       <c r="B464" t="s">
-        <v>462</v>
+        <v>487</v>
       </c>
       <c r="C464">
         <v>0</v>
@@ -39204,7 +39380,7 @@
         <v>464</v>
       </c>
       <c r="B465" t="s">
-        <v>463</v>
+        <v>488</v>
       </c>
       <c r="C465">
         <v>0</v>
@@ -39284,7 +39460,7 @@
         <v>465</v>
       </c>
       <c r="B466" t="s">
-        <v>464</v>
+        <v>489</v>
       </c>
       <c r="C466">
         <v>0</v>
@@ -39364,7 +39540,7 @@
         <v>466</v>
       </c>
       <c r="B467" t="s">
-        <v>465</v>
+        <v>490</v>
       </c>
       <c r="C467">
         <v>0</v>
@@ -39444,7 +39620,7 @@
         <v>467</v>
       </c>
       <c r="B468" t="s">
-        <v>466</v>
+        <v>491</v>
       </c>
       <c r="C468">
         <v>0</v>
@@ -39524,7 +39700,7 @@
         <v>468</v>
       </c>
       <c r="B469" t="s">
-        <v>467</v>
+        <v>492</v>
       </c>
       <c r="C469">
         <v>0</v>
@@ -39604,7 +39780,7 @@
         <v>469</v>
       </c>
       <c r="B470" t="s">
-        <v>468</v>
+        <v>493</v>
       </c>
       <c r="C470">
         <v>0</v>
@@ -39684,7 +39860,7 @@
         <v>470</v>
       </c>
       <c r="B471" t="s">
-        <v>469</v>
+        <v>494</v>
       </c>
       <c r="C471">
         <v>0</v>
@@ -39764,7 +39940,7 @@
         <v>471</v>
       </c>
       <c r="B472" t="s">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="C472">
         <v>0</v>
@@ -39844,7 +40020,7 @@
         <v>472</v>
       </c>
       <c r="B473" t="s">
-        <v>471</v>
+        <v>496</v>
       </c>
       <c r="C473">
         <v>0</v>
@@ -39924,7 +40100,7 @@
         <v>473</v>
       </c>
       <c r="B474" t="s">
-        <v>472</v>
+        <v>497</v>
       </c>
       <c r="C474">
         <v>0</v>
@@ -40004,7 +40180,7 @@
         <v>474</v>
       </c>
       <c r="B475" t="s">
-        <v>473</v>
+        <v>498</v>
       </c>
       <c r="C475">
         <v>0</v>
@@ -40084,7 +40260,7 @@
         <v>475</v>
       </c>
       <c r="B476" t="s">
-        <v>474</v>
+        <v>499</v>
       </c>
       <c r="C476">
         <v>0</v>
@@ -40164,7 +40340,7 @@
         <v>476</v>
       </c>
       <c r="B477" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="C477">
         <v>0</v>
@@ -40244,7 +40420,7 @@
         <v>477</v>
       </c>
       <c r="B478" t="s">
-        <v>476</v>
+        <v>501</v>
       </c>
       <c r="C478">
         <v>0</v>
@@ -40324,7 +40500,7 @@
         <v>478</v>
       </c>
       <c r="B479" t="s">
-        <v>477</v>
+        <v>502</v>
       </c>
       <c r="C479">
         <v>0</v>
@@ -40404,7 +40580,7 @@
         <v>479</v>
       </c>
       <c r="B480" t="s">
-        <v>478</v>
+        <v>503</v>
       </c>
       <c r="C480">
         <v>0</v>
@@ -40484,7 +40660,7 @@
         <v>480</v>
       </c>
       <c r="B481" t="s">
-        <v>479</v>
+        <v>504</v>
       </c>
       <c r="C481">
         <v>0</v>
@@ -40564,7 +40740,7 @@
         <v>481</v>
       </c>
       <c r="B482" t="s">
-        <v>480</v>
+        <v>505</v>
       </c>
       <c r="C482">
         <v>0</v>
@@ -40644,7 +40820,7 @@
         <v>482</v>
       </c>
       <c r="B483" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="C483">
         <v>0</v>
@@ -40724,7 +40900,7 @@
         <v>483</v>
       </c>
       <c r="B484" t="s">
-        <v>482</v>
+        <v>507</v>
       </c>
       <c r="C484">
         <v>0</v>
@@ -40804,7 +40980,7 @@
         <v>484</v>
       </c>
       <c r="B485" t="s">
-        <v>483</v>
+        <v>508</v>
       </c>
       <c r="C485">
         <v>0</v>
@@ -40884,7 +41060,7 @@
         <v>485</v>
       </c>
       <c r="B486" t="s">
-        <v>484</v>
+        <v>509</v>
       </c>
       <c r="C486">
         <v>0</v>
@@ -40964,7 +41140,7 @@
         <v>486</v>
       </c>
       <c r="B487" t="s">
-        <v>485</v>
+        <v>510</v>
       </c>
       <c r="C487">
         <v>0</v>
@@ -41044,7 +41220,7 @@
         <v>487</v>
       </c>
       <c r="B488" t="s">
-        <v>486</v>
+        <v>511</v>
       </c>
       <c r="C488">
         <v>0</v>
@@ -41124,7 +41300,7 @@
         <v>488</v>
       </c>
       <c r="B489" t="s">
-        <v>487</v>
+        <v>512</v>
       </c>
       <c r="C489">
         <v>0</v>
@@ -41204,7 +41380,7 @@
         <v>489</v>
       </c>
       <c r="B490" t="s">
-        <v>488</v>
+        <v>513</v>
       </c>
       <c r="C490">
         <v>0</v>
@@ -41284,7 +41460,7 @@
         <v>490</v>
       </c>
       <c r="B491" t="s">
-        <v>489</v>
+        <v>514</v>
       </c>
       <c r="C491">
         <v>0</v>
@@ -41364,7 +41540,7 @@
         <v>491</v>
       </c>
       <c r="B492" t="s">
-        <v>490</v>
+        <v>515</v>
       </c>
       <c r="C492">
         <v>0</v>
@@ -41444,7 +41620,7 @@
         <v>492</v>
       </c>
       <c r="B493" t="s">
-        <v>491</v>
+        <v>516</v>
       </c>
       <c r="C493">
         <v>0</v>
@@ -41524,7 +41700,7 @@
         <v>493</v>
       </c>
       <c r="B494" t="s">
-        <v>492</v>
+        <v>517</v>
       </c>
       <c r="C494">
         <v>0</v>
@@ -41604,7 +41780,7 @@
         <v>494</v>
       </c>
       <c r="B495" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
       <c r="C495">
         <v>0</v>
@@ -41684,7 +41860,7 @@
         <v>495</v>
       </c>
       <c r="B496" t="s">
-        <v>494</v>
+        <v>519</v>
       </c>
       <c r="C496">
         <v>0</v>
@@ -41764,7 +41940,7 @@
         <v>496</v>
       </c>
       <c r="B497" t="s">
-        <v>495</v>
+        <v>520</v>
       </c>
       <c r="C497">
         <v>0</v>
@@ -41844,7 +42020,7 @@
         <v>497</v>
       </c>
       <c r="B498" t="s">
-        <v>496</v>
+        <v>521</v>
       </c>
       <c r="C498">
         <v>0</v>
@@ -41924,7 +42100,7 @@
         <v>498</v>
       </c>
       <c r="B499" t="s">
-        <v>497</v>
+        <v>522</v>
       </c>
       <c r="C499">
         <v>0</v>
@@ -42004,7 +42180,7 @@
         <v>499</v>
       </c>
       <c r="B500" t="s">
-        <v>498</v>
+        <v>523</v>
       </c>
       <c r="C500">
         <v>0</v>
@@ -42084,7 +42260,7 @@
         <v>500</v>
       </c>
       <c r="B501" t="s">
-        <v>499</v>
+        <v>524</v>
       </c>
       <c r="C501">
         <v>0</v>
@@ -42164,7 +42340,7 @@
         <v>501</v>
       </c>
       <c r="B502" t="s">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="C502">
         <v>0</v>
@@ -42244,7 +42420,7 @@
         <v>502</v>
       </c>
       <c r="B503" t="s">
-        <v>501</v>
+        <v>526</v>
       </c>
       <c r="C503">
         <v>0</v>
@@ -42324,7 +42500,7 @@
         <v>503</v>
       </c>
       <c r="B504" t="s">
-        <v>502</v>
+        <v>527</v>
       </c>
       <c r="C504">
         <v>0</v>
@@ -42404,7 +42580,7 @@
         <v>504</v>
       </c>
       <c r="B505" t="s">
-        <v>503</v>
+        <v>528</v>
       </c>
       <c r="C505">
         <v>0</v>
@@ -42484,7 +42660,7 @@
         <v>505</v>
       </c>
       <c r="B506" t="s">
-        <v>504</v>
+        <v>529</v>
       </c>
       <c r="C506">
         <v>0</v>
@@ -42564,7 +42740,7 @@
         <v>506</v>
       </c>
       <c r="B507" t="s">
-        <v>505</v>
+        <v>530</v>
       </c>
       <c r="C507">
         <v>0</v>
@@ -42644,7 +42820,7 @@
         <v>507</v>
       </c>
       <c r="B508" t="s">
-        <v>506</v>
+        <v>531</v>
       </c>
       <c r="C508">
         <v>0</v>
@@ -42724,7 +42900,7 @@
         <v>508</v>
       </c>
       <c r="B509" t="s">
-        <v>507</v>
+        <v>532</v>
       </c>
       <c r="C509">
         <v>0</v>
@@ -42804,7 +42980,7 @@
         <v>509</v>
       </c>
       <c r="B510" t="s">
-        <v>508</v>
+        <v>533</v>
       </c>
       <c r="C510">
         <v>0</v>
@@ -42884,7 +43060,7 @@
         <v>510</v>
       </c>
       <c r="B511" t="s">
-        <v>509</v>
+        <v>534</v>
       </c>
       <c r="C511">
         <v>0</v>
@@ -42964,7 +43140,7 @@
         <v>511</v>
       </c>
       <c r="B512" t="s">
-        <v>510</v>
+        <v>535</v>
       </c>
       <c r="C512">
         <v>0</v>
@@ -43044,7 +43220,7 @@
         <v>512</v>
       </c>
       <c r="B513" t="s">
-        <v>511</v>
+        <v>536</v>
       </c>
       <c r="C513">
         <v>0</v>
@@ -43124,7 +43300,7 @@
         <v>513</v>
       </c>
       <c r="B514" t="s">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="C514">
         <v>0</v>
@@ -43204,7 +43380,7 @@
         <v>514</v>
       </c>
       <c r="B515" t="s">
-        <v>513</v>
+        <v>538</v>
       </c>
       <c r="C515">
         <v>0</v>
@@ -43284,7 +43460,7 @@
         <v>515</v>
       </c>
       <c r="B516" t="s">
-        <v>514</v>
+        <v>539</v>
       </c>
       <c r="C516">
         <v>0</v>
@@ -43364,7 +43540,7 @@
         <v>516</v>
       </c>
       <c r="B517" t="s">
-        <v>515</v>
+        <v>540</v>
       </c>
       <c r="C517">
         <v>0</v>
@@ -43444,7 +43620,7 @@
         <v>517</v>
       </c>
       <c r="B518" t="s">
-        <v>516</v>
+        <v>541</v>
       </c>
       <c r="C518">
         <v>0</v>
@@ -43524,7 +43700,7 @@
         <v>518</v>
       </c>
       <c r="B519" t="s">
-        <v>517</v>
+        <v>542</v>
       </c>
       <c r="C519">
         <v>0</v>
@@ -43604,7 +43780,7 @@
         <v>519</v>
       </c>
       <c r="B520" t="s">
-        <v>518</v>
+        <v>543</v>
       </c>
       <c r="C520">
         <v>0</v>
@@ -43684,7 +43860,7 @@
         <v>520</v>
       </c>
       <c r="B521" t="s">
-        <v>519</v>
+        <v>544</v>
       </c>
       <c r="C521">
         <v>0</v>
@@ -43764,7 +43940,7 @@
         <v>521</v>
       </c>
       <c r="B522" t="s">
-        <v>520</v>
+        <v>545</v>
       </c>
       <c r="C522">
         <v>0</v>
@@ -43844,7 +44020,7 @@
         <v>522</v>
       </c>
       <c r="B523" t="s">
-        <v>521</v>
+        <v>546</v>
       </c>
       <c r="C523">
         <v>0</v>
@@ -43924,7 +44100,7 @@
         <v>523</v>
       </c>
       <c r="B524" t="s">
-        <v>522</v>
+        <v>547</v>
       </c>
       <c r="C524">
         <v>0</v>
@@ -44004,7 +44180,7 @@
         <v>524</v>
       </c>
       <c r="B525" t="s">
-        <v>523</v>
+        <v>548</v>
       </c>
       <c r="C525">
         <v>0</v>
@@ -44084,7 +44260,7 @@
         <v>525</v>
       </c>
       <c r="B526" t="s">
-        <v>524</v>
+        <v>549</v>
       </c>
       <c r="C526">
         <v>0</v>
@@ -44164,7 +44340,7 @@
         <v>526</v>
       </c>
       <c r="B527" t="s">
-        <v>525</v>
+        <v>550</v>
       </c>
       <c r="C527">
         <v>0</v>
@@ -44244,7 +44420,7 @@
         <v>527</v>
       </c>
       <c r="B528" t="s">
-        <v>526</v>
+        <v>551</v>
       </c>
       <c r="C528">
         <v>0</v>
@@ -44324,7 +44500,7 @@
         <v>528</v>
       </c>
       <c r="B529" t="s">
-        <v>527</v>
+        <v>552</v>
       </c>
       <c r="C529">
         <v>0</v>
@@ -44404,7 +44580,7 @@
         <v>529</v>
       </c>
       <c r="B530" t="s">
-        <v>528</v>
+        <v>553</v>
       </c>
       <c r="C530">
         <v>0</v>
@@ -44484,7 +44660,7 @@
         <v>530</v>
       </c>
       <c r="B531" t="s">
-        <v>529</v>
+        <v>554</v>
       </c>
       <c r="C531">
         <v>0</v>
@@ -44564,7 +44740,7 @@
         <v>531</v>
       </c>
       <c r="B532" t="s">
-        <v>530</v>
+        <v>555</v>
       </c>
       <c r="C532">
         <v>0</v>
@@ -44644,7 +44820,7 @@
         <v>532</v>
       </c>
       <c r="B533" t="s">
-        <v>531</v>
+        <v>556</v>
       </c>
       <c r="C533">
         <v>0</v>
@@ -44724,7 +44900,7 @@
         <v>533</v>
       </c>
       <c r="B534" t="s">
-        <v>532</v>
+        <v>557</v>
       </c>
       <c r="C534">
         <v>0</v>
@@ -44804,7 +44980,7 @@
         <v>534</v>
       </c>
       <c r="B535" t="s">
-        <v>533</v>
+        <v>558</v>
       </c>
       <c r="C535">
         <v>0</v>
@@ -44884,7 +45060,7 @@
         <v>535</v>
       </c>
       <c r="B536" t="s">
-        <v>534</v>
+        <v>559</v>
       </c>
       <c r="C536">
         <v>0</v>
@@ -44964,7 +45140,7 @@
         <v>536</v>
       </c>
       <c r="B537" t="s">
-        <v>535</v>
+        <v>560</v>
       </c>
       <c r="C537">
         <v>0</v>
@@ -45044,7 +45220,7 @@
         <v>537</v>
       </c>
       <c r="B538" t="s">
-        <v>536</v>
+        <v>561</v>
       </c>
       <c r="C538">
         <v>0</v>
@@ -45124,7 +45300,7 @@
         <v>538</v>
       </c>
       <c r="B539" t="s">
-        <v>537</v>
+        <v>562</v>
       </c>
       <c r="C539">
         <v>0</v>
@@ -45204,7 +45380,7 @@
         <v>539</v>
       </c>
       <c r="B540" t="s">
-        <v>538</v>
+        <v>563</v>
       </c>
       <c r="C540">
         <v>0</v>
@@ -45284,7 +45460,7 @@
         <v>540</v>
       </c>
       <c r="B541" t="s">
-        <v>539</v>
+        <v>564</v>
       </c>
       <c r="C541">
         <v>0</v>
@@ -45364,7 +45540,7 @@
         <v>541</v>
       </c>
       <c r="B542" t="s">
-        <v>540</v>
+        <v>565</v>
       </c>
       <c r="C542">
         <v>0</v>
@@ -45444,7 +45620,7 @@
         <v>542</v>
       </c>
       <c r="B543" t="s">
-        <v>541</v>
+        <v>566</v>
       </c>
       <c r="C543">
         <v>0</v>
@@ -45524,7 +45700,7 @@
         <v>543</v>
       </c>
       <c r="B544" t="s">
-        <v>542</v>
+        <v>567</v>
       </c>
       <c r="C544">
         <v>0</v>
@@ -45604,7 +45780,7 @@
         <v>544</v>
       </c>
       <c r="B545" t="s">
-        <v>543</v>
+        <v>568</v>
       </c>
       <c r="C545">
         <v>0</v>
@@ -45684,7 +45860,7 @@
         <v>545</v>
       </c>
       <c r="B546" t="s">
-        <v>544</v>
+        <v>569</v>
       </c>
       <c r="C546">
         <v>0</v>
@@ -45764,7 +45940,7 @@
         <v>546</v>
       </c>
       <c r="B547" t="s">
-        <v>545</v>
+        <v>570</v>
       </c>
       <c r="C547">
         <v>0</v>
@@ -45844,7 +46020,7 @@
         <v>547</v>
       </c>
       <c r="B548" t="s">
-        <v>546</v>
+        <v>571</v>
       </c>
       <c r="C548">
         <v>0</v>
@@ -45924,7 +46100,7 @@
         <v>548</v>
       </c>
       <c r="B549" t="s">
-        <v>547</v>
+        <v>572</v>
       </c>
       <c r="C549">
         <v>0</v>
@@ -46004,7 +46180,7 @@
         <v>550</v>
       </c>
       <c r="B550" t="s">
-        <v>548</v>
+        <v>573</v>
       </c>
       <c r="C550">
         <v>0</v>
@@ -46084,7 +46260,7 @@
         <v>551</v>
       </c>
       <c r="B551" t="s">
-        <v>549</v>
+        <v>574</v>
       </c>
       <c r="C551">
         <v>0</v>
@@ -46164,7 +46340,7 @@
         <v>552</v>
       </c>
       <c r="B552" t="s">
-        <v>550</v>
+        <v>575</v>
       </c>
       <c r="C552">
         <v>0</v>
@@ -46244,7 +46420,7 @@
         <v>553</v>
       </c>
       <c r="B553" t="s">
-        <v>551</v>
+        <v>576</v>
       </c>
       <c r="C553">
         <v>0</v>
@@ -46324,7 +46500,7 @@
         <v>554</v>
       </c>
       <c r="B554" t="s">
-        <v>552</v>
+        <v>577</v>
       </c>
       <c r="C554">
         <v>0</v>
@@ -46404,7 +46580,7 @@
         <v>555</v>
       </c>
       <c r="B555" t="s">
-        <v>553</v>
+        <v>578</v>
       </c>
       <c r="C555">
         <v>0</v>
@@ -46484,7 +46660,7 @@
         <v>556</v>
       </c>
       <c r="B556" t="s">
-        <v>554</v>
+        <v>579</v>
       </c>
       <c r="C556">
         <v>0</v>
@@ -46564,7 +46740,7 @@
         <v>557</v>
       </c>
       <c r="B557" t="s">
-        <v>555</v>
+        <v>580</v>
       </c>
       <c r="C557">
         <v>0</v>
@@ -46644,7 +46820,7 @@
         <v>558</v>
       </c>
       <c r="B558" t="s">
-        <v>556</v>
+        <v>581</v>
       </c>
       <c r="C558">
         <v>0</v>
@@ -46724,7 +46900,7 @@
         <v>559</v>
       </c>
       <c r="B559" t="s">
-        <v>557</v>
+        <v>582</v>
       </c>
       <c r="C559">
         <v>0</v>
@@ -46804,7 +46980,7 @@
         <v>560</v>
       </c>
       <c r="B560" t="s">
-        <v>558</v>
+        <v>583</v>
       </c>
       <c r="C560">
         <v>0</v>
@@ -46884,7 +47060,7 @@
         <v>561</v>
       </c>
       <c r="B561" t="s">
-        <v>559</v>
+        <v>584</v>
       </c>
       <c r="C561">
         <v>0</v>
@@ -46964,7 +47140,7 @@
         <v>562</v>
       </c>
       <c r="B562" t="s">
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="C562">
         <v>0</v>
@@ -47044,7 +47220,7 @@
         <v>563</v>
       </c>
       <c r="B563" t="s">
-        <v>561</v>
+        <v>586</v>
       </c>
       <c r="C563">
         <v>0</v>
@@ -47124,7 +47300,7 @@
         <v>564</v>
       </c>
       <c r="B564" t="s">
-        <v>562</v>
+        <v>587</v>
       </c>
       <c r="C564">
         <v>0</v>
@@ -47204,7 +47380,7 @@
         <v>565</v>
       </c>
       <c r="B565" t="s">
-        <v>563</v>
+        <v>588</v>
       </c>
       <c r="C565">
         <v>0</v>
@@ -47284,7 +47460,7 @@
         <v>566</v>
       </c>
       <c r="B566" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="C566">
         <v>0</v>
@@ -47364,7 +47540,7 @@
         <v>567</v>
       </c>
       <c r="B567" t="s">
-        <v>565</v>
+        <v>590</v>
       </c>
       <c r="C567">
         <v>0</v>
@@ -47444,7 +47620,7 @@
         <v>568</v>
       </c>
       <c r="B568" t="s">
-        <v>566</v>
+        <v>591</v>
       </c>
       <c r="C568">
         <v>0</v>
@@ -47524,7 +47700,7 @@
         <v>569</v>
       </c>
       <c r="B569" t="s">
-        <v>567</v>
+        <v>592</v>
       </c>
       <c r="C569">
         <v>0</v>
@@ -47604,7 +47780,7 @@
         <v>570</v>
       </c>
       <c r="B570" t="s">
-        <v>568</v>
+        <v>593</v>
       </c>
       <c r="C570">
         <v>0</v>
@@ -47684,7 +47860,7 @@
         <v>571</v>
       </c>
       <c r="B571" t="s">
-        <v>569</v>
+        <v>594</v>
       </c>
       <c r="C571">
         <v>0</v>
@@ -47764,7 +47940,7 @@
         <v>572</v>
       </c>
       <c r="B572" t="s">
-        <v>570</v>
+        <v>595</v>
       </c>
       <c r="C572">
         <v>0</v>
@@ -47844,7 +48020,7 @@
         <v>573</v>
       </c>
       <c r="B573" t="s">
-        <v>571</v>
+        <v>596</v>
       </c>
       <c r="C573">
         <v>0</v>
@@ -47924,7 +48100,7 @@
         <v>574</v>
       </c>
       <c r="B574" t="s">
-        <v>572</v>
+        <v>597</v>
       </c>
       <c r="C574">
         <v>0</v>
@@ -48004,7 +48180,7 @@
         <v>575</v>
       </c>
       <c r="B575" t="s">
-        <v>573</v>
+        <v>598</v>
       </c>
       <c r="C575">
         <v>0</v>
@@ -48084,7 +48260,7 @@
         <v>576</v>
       </c>
       <c r="B576" t="s">
-        <v>574</v>
+        <v>599</v>
       </c>
       <c r="C576">
         <v>0</v>
@@ -48164,7 +48340,7 @@
         <v>577</v>
       </c>
       <c r="B577" t="s">
-        <v>575</v>
+        <v>600</v>
       </c>
       <c r="C577">
         <v>0</v>
@@ -48244,7 +48420,7 @@
         <v>578</v>
       </c>
       <c r="B578" t="s">
-        <v>576</v>
+        <v>601</v>
       </c>
       <c r="C578">
         <v>0</v>
@@ -48324,7 +48500,7 @@
         <v>579</v>
       </c>
       <c r="B579" t="s">
-        <v>577</v>
+        <v>602</v>
       </c>
       <c r="C579">
         <v>0</v>
